--- a/res/csv/evaluation.xlsx
+++ b/res/csv/evaluation.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB99"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -489,6 +489,7 @@
     <col width="7" customWidth="1" min="26" max="26"/>
     <col width="70" customWidth="1" min="27" max="27"/>
     <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -632,6 +633,11 @@
           <t>figures</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -748,6 +754,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -864,6 +875,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -980,6 +996,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1096,6 +1117,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1212,6 +1238,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1328,6 +1359,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1444,6 +1480,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1560,6 +1601,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1676,6 +1722,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1792,6 +1843,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1908,6 +1964,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2024,6 +2085,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2140,6 +2206,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2256,6 +2327,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2376,6 +2452,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2496,6 +2577,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2616,6 +2702,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2736,6 +2827,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -2856,6 +2952,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2976,6 +3077,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -3096,6 +3202,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3216,6 +3327,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3336,6 +3452,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3456,6 +3577,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3576,6 +3702,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3696,6 +3827,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3816,6 +3952,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3936,6 +4077,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -4056,6 +4202,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -4176,6 +4327,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -4296,6 +4452,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -4416,6 +4577,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -4536,6 +4702,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -4656,6 +4827,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -4776,6 +4952,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -4896,6 +5077,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -5016,6 +5202,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -5136,6 +5327,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -5256,6 +5452,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -5376,6 +5577,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -5496,6 +5702,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -5616,6 +5827,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5732,6 +5948,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5848,6 +6069,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5964,6 +6190,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6080,6 +6311,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -6200,6 +6436,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC48" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -6320,6 +6561,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC49" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6436,6 +6682,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6552,6 +6803,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6668,6 +6924,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6784,6 +7045,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6900,6 +7166,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7016,6 +7287,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7132,6 +7408,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7248,6 +7529,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7364,6 +7650,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -7484,6 +7775,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC59" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7600,6 +7896,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -7720,6 +8021,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC61" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7836,6 +8142,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -7956,6 +8267,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC63" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8072,6 +8388,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8188,6 +8509,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8304,6 +8630,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -8424,6 +8755,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC67" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8540,6 +8876,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8656,6 +8997,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8772,6 +9118,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8888,6 +9239,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9004,6 +9360,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9120,6 +9481,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9236,6 +9602,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9352,6 +9723,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9468,6 +9844,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9584,6 +9965,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9700,6 +10086,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9816,6 +10207,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9932,6 +10328,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10048,6 +10449,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10164,6 +10570,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10280,6 +10691,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10396,6 +10812,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10512,6 +10933,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -10632,6 +11058,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC86" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10748,6 +11179,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10864,6 +11300,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10980,6 +11421,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11096,6 +11542,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11212,6 +11663,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -11332,6 +11788,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC92" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11448,6 +11909,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11564,6 +12030,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11680,6 +12151,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11796,6 +12272,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -11916,6 +12397,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC97" s="6" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12032,6 +12518,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12146,109 +12637,212 @@
       <c r="AB99" s="2" t="inlineStr">
         <is>
           <t>open</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>view</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC99" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
